--- a/artfynd/A 54504-2022 artfynd.xlsx
+++ b/artfynd/A 54504-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54504-2022 artfynd.xlsx
+++ b/artfynd/A 54504-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1374,113 +1374,6 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>112605438</v>
-      </c>
-      <c r="B8" t="n">
-        <v>77856</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ekfors, Nb</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>875098</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7379994</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Övertorneå</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Hietaniemi</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54504-2022 artfynd.xlsx
+++ b/artfynd/A 54504-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104766434</v>
+        <v>112605386</v>
       </c>
       <c r="B2" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Övertorneå, Nb</t>
+          <t>Ekfors, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>875296.6966927222</v>
+        <v>875082</v>
       </c>
       <c r="R2" t="n">
-        <v>7379778.8591036</v>
+        <v>7379943</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2022-11-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2022-11-03</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -791,12 +780,7 @@
         <v>104788926</v>
       </c>
       <c r="B3" t="n">
-        <v>89794</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,12 +797,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rigidoporus corticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pouzar</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>875130.887204794</v>
+        <v>875131</v>
       </c>
       <c r="R3" t="n">
-        <v>7379945.556653732</v>
+        <v>7379946</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,19 +852,9 @@
           <t>2022-11-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,61 +882,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104788873</v>
+        <v>112605438</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jyppyräs sluttning, Nb</t>
+          <t>Ekfors, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>875130.887204794</v>
+        <v>875097</v>
       </c>
       <c r="R4" t="n">
-        <v>7379945.556653732</v>
+        <v>7379994</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,27 +947,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-11-01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hackspår av spillkråka.</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,27 +972,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104765927</v>
+        <v>104766434</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,21 +995,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>875293.0732413747</v>
+        <v>875296</v>
       </c>
       <c r="R5" t="n">
-        <v>7379760.476412775</v>
+        <v>7379778</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1055,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1065,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,15 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104766298</v>
+        <v>104788873</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1162,38 +1103,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Övertorneå, Nb</t>
+          <t>Jyppyräs sluttning, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>875296.6966927222</v>
+        <v>875131</v>
       </c>
       <c r="R6" t="n">
-        <v>7379778.8591036</v>
+        <v>7379946</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,19 +1168,14 @@
           <t>2022-11-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:02</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hackspår av spillkråka.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,65 +1190,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Persson, Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109910757</v>
+        <v>104765927</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ekfors, Nb</t>
+          <t>Övertorneå, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>875098.2911684301</v>
+        <v>875293</v>
       </c>
       <c r="R7" t="n">
-        <v>7379994.017015507</v>
+        <v>7379761</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,27 +1268,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-01</t>
+          <t>2022-11-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,15 +1298,123 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104766298</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Övertorneå, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>875296</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7379778</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hietaniemi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-11-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-11-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Viktoria Sturk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54504-2022 artfynd.xlsx
+++ b/artfynd/A 54504-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605386</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104788926</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112605438</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1089,6 +1109,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104766434</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104788873</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104765927</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1415,8 +1450,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104766298</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>